--- a/examples/by_plot_type/neighborhood_enrichment/data.xlsx
+++ b/examples/by_plot_type/neighborhood_enrichment/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,14 +458,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tumor</t>
+          <t>CT_00</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.094865</v>
+        <v>-2.09734608719831</v>
       </c>
       <c r="D2" t="n">
-        <v>0.533983</v>
+        <v>0.0438709142880815</v>
       </c>
     </row>
     <row r="3">
@@ -476,14 +476,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stroma</t>
+          <t>CT_01</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.636582</v>
+        <v>0.887369083790183</v>
       </c>
       <c r="D3" t="n">
-        <v>0.19433</v>
+        <v>0.0029412983139318</v>
       </c>
     </row>
     <row r="4">
@@ -494,14 +494,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Macrophage</t>
+          <t>CT_02</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-1.464946</v>
+        <v>0.163493525120144</v>
       </c>
       <c r="D4" t="n">
-        <v>0.045281</v>
+        <v>0.008016073573884499</v>
       </c>
     </row>
     <row r="5">
@@ -512,14 +512,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CD8 T cell</t>
+          <t>CT_03</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-1.464946</v>
+        <v>-2.34560990173994</v>
       </c>
       <c r="D5" t="n">
-        <v>0.045281</v>
+        <v>0.0218940304072248</v>
       </c>
     </row>
     <row r="6">
@@ -530,14 +530,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CD4 T cell</t>
+          <t>CT_04</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1.464946</v>
+        <v>-0.77744640982582</v>
       </c>
       <c r="D6" t="n">
-        <v>0.045281</v>
+        <v>0.0007663946310949</v>
       </c>
     </row>
     <row r="7">
@@ -548,14 +548,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B cell</t>
+          <t>CT_05</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-1.464946</v>
+        <v>0.384133127503192</v>
       </c>
       <c r="D7" t="n">
-        <v>0.045281</v>
+        <v>0.0094452959940345</v>
       </c>
     </row>
     <row r="8">
@@ -566,14 +566,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Endothelial</t>
+          <t>CT_06</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-1.464946</v>
+        <v>1.24431460562196</v>
       </c>
       <c r="D8" t="n">
-        <v>0.045281</v>
+        <v>0.0615808442768963</v>
       </c>
     </row>
     <row r="9">
@@ -584,1166 +584,4406 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fibroblast</t>
+          <t>CT_07</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1.464946</v>
+        <v>1.56049752919855</v>
       </c>
       <c r="D9" t="n">
-        <v>0.045281</v>
+        <v>0.196342019139152</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CN2</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tumor</t>
+          <t>CT_08</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-1.562025</v>
+        <v>1.27080513924183</v>
       </c>
       <c r="D10" t="n">
-        <v>0.042334</v>
+        <v>0.160777165582667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CN2</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stroma</t>
+          <t>CT_09</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.060467</v>
+        <v>-0.596097103632784</v>
       </c>
       <c r="D11" t="n">
-        <v>0.521401</v>
+        <v>0.104416090144579</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CN2</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Macrophage</t>
+          <t>CT_10</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.845378</v>
+        <v>1.01990581930065</v>
       </c>
       <c r="D12" t="n">
-        <v>0.224592</v>
+        <v>0.06887194995650189</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CN2</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CD8 T cell</t>
+          <t>CT_11</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1.562025</v>
+        <v>0.360207671152485</v>
       </c>
       <c r="D13" t="n">
-        <v>0.042334</v>
+        <v>0.0142922242014996</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CN2</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CD4 T cell</t>
+          <t>CT_12</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-1.562025</v>
+        <v>0.698320185491184</v>
       </c>
       <c r="D14" t="n">
-        <v>0.042334</v>
+        <v>0.0139400969385641</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CN2</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B cell</t>
+          <t>CT_13</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-1.562025</v>
+        <v>-0.889535967254113</v>
       </c>
       <c r="D15" t="n">
-        <v>0.042334</v>
+        <v>0.0434152201831061</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CN2</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Endothelial</t>
+          <t>CT_14</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-1.562025</v>
+        <v>0.281190514159369</v>
       </c>
       <c r="D16" t="n">
-        <v>0.042334</v>
+        <v>0.0008906748415427</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CN2</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fibroblast</t>
+          <t>CT_15</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-1.562025</v>
+        <v>0.0264673276243051</v>
       </c>
       <c r="D17" t="n">
-        <v>0.042334</v>
+        <v>0.047744314180372</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CN3</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tumor</t>
+          <t>CT_16</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-1.73541</v>
+        <v>0.275875077525625</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03754</v>
+        <v>0.0031277186296035</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CN3</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stroma</t>
+          <t>CT_17</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-1.73541</v>
+        <v>-1.17911599422116</v>
       </c>
       <c r="D19" t="n">
-        <v>0.03754</v>
+        <v>0.0026513111562202</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CN3</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Macrophage</t>
+          <t>CT_18</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.151566</v>
+        <v>-1.0639320430434</v>
       </c>
       <c r="D20" t="n">
-        <v>0.555387</v>
+        <v>0.0422552715522598</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CN3</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CD8 T cell</t>
+          <t>CT_19</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.811438</v>
+        <v>-0.570241530102551</v>
       </c>
       <c r="D21" t="n">
-        <v>0.21937</v>
+        <v>0.0056754629437839</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CN3</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CD4 T cell</t>
+          <t>CT_20</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-1.73541</v>
+        <v>1.27810118984124</v>
       </c>
       <c r="D22" t="n">
-        <v>0.03754</v>
+        <v>0.0031277186296035</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CN3</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B cell</t>
+          <t>CT_21</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-1.73541</v>
+        <v>1.94788001669443</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03754</v>
+        <v>0.012593727992046</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CN3</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Endothelial</t>
+          <t>CT_22</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-1.73541</v>
+        <v>1.93508503667758</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03754</v>
+        <v>0.0474336136542524</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CN3</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fibroblast</t>
+          <t>CT_23</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-1.73541</v>
+        <v>2.08587856888621</v>
       </c>
       <c r="D25" t="n">
-        <v>0.03754</v>
+        <v>0.0011392352624383</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CN4</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tumor</t>
+          <t>CT_24</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-1.791133</v>
+        <v>-0.0699402173224396</v>
       </c>
       <c r="D26" t="n">
-        <v>0.036118</v>
+        <v>0.0001449935788557</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CN4</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Stroma</t>
+          <t>CT_25</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-1.791133</v>
+        <v>0.9376572007512159</v>
       </c>
       <c r="D27" t="n">
-        <v>0.036118</v>
+        <v>0.0014499357885579</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CN4</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Macrophage</t>
+          <t>CT_26</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-1.791133</v>
+        <v>1.7303185014934</v>
       </c>
       <c r="D28" t="n">
-        <v>0.036118</v>
+        <v>0.0305522184017564</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CN4</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CD8 T cell</t>
+          <t>CT_27</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.186084</v>
+        <v>-0.043852400630981</v>
       </c>
       <c r="D29" t="n">
-        <v>0.568836</v>
+        <v>0.0506441857574878</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CN4</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CD4 T cell</t>
+          <t>CT_00</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.778751</v>
+        <v>2.29387558728421</v>
       </c>
       <c r="D30" t="n">
-        <v>0.214456</v>
+        <v>0.920675264363488</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CN4</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B cell</t>
+          <t>CT_01</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-1.791133</v>
+        <v>-2.66291069960037</v>
       </c>
       <c r="D31" t="n">
-        <v>0.036118</v>
+        <v>0.0002510276444193</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CN4</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Endothelial</t>
+          <t>CT_02</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-1.791133</v>
+        <v>-0.693901554959844</v>
       </c>
       <c r="D32" t="n">
-        <v>0.036118</v>
+        <v>0.0044243622328908</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CN4</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fibroblast</t>
+          <t>CT_03</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-1.791133</v>
+        <v>-4.45148391096422</v>
       </c>
       <c r="D33" t="n">
-        <v>0.036118</v>
+        <v>0.0050833097994916</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CN5</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tumor</t>
+          <t>CT_04</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-1.738608</v>
+        <v>-4.38680690546993</v>
       </c>
       <c r="D34" t="n">
-        <v>0.037457</v>
+        <v>6.27569111048354e-05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CN5</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Stroma</t>
+          <t>CT_05</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-1.738608</v>
+        <v>-1.14904289785783</v>
       </c>
       <c r="D35" t="n">
-        <v>0.037457</v>
+        <v>0.0032633593774514</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CN5</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Macrophage</t>
+          <t>CT_06</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-1.738608</v>
+        <v>-2.82351977866271</v>
       </c>
       <c r="D36" t="n">
-        <v>0.037457</v>
+        <v>0.0036712792996328</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CN5</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CD8 T cell</t>
+          <t>CT_07</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-1.738608</v>
+        <v>-3.86035280341557</v>
       </c>
       <c r="D37" t="n">
-        <v>0.037457</v>
+        <v>0.0045812545106529</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CN5</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CD4 T cell</t>
+          <t>CT_08</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.135203</v>
+        <v>-3.18762454209941</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5491239999999999</v>
+        <v>0.0073111801437133</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CN5</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B cell</t>
+          <t>CT_09</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.85524</v>
+        <v>-3.85284204149279</v>
       </c>
       <c r="D39" t="n">
-        <v>0.226132</v>
+        <v>0.0109197025322413</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CN5</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Endothelial</t>
+          <t>CT_10</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-1.738608</v>
+        <v>-5.43423593501236</v>
       </c>
       <c r="D40" t="n">
-        <v>0.037457</v>
+        <v>0.0007844613888104</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CN5</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fibroblast</t>
+          <t>CT_11</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-1.738608</v>
+        <v>-3.8854397295815</v>
       </c>
       <c r="D41" t="n">
-        <v>0.037457</v>
+        <v>0.000753082933258</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CN6</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tumor</t>
+          <t>CT_12</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-1.596393</v>
+        <v>-2.77472623184488</v>
       </c>
       <c r="D42" t="n">
-        <v>0.041338</v>
+        <v>0.0012551382220967</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CN6</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stroma</t>
+          <t>CT_13</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-1.596393</v>
+        <v>-3.10910778553096</v>
       </c>
       <c r="D43" t="n">
-        <v>0.041338</v>
+        <v>0.009319401299067999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CN6</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Macrophage</t>
+          <t>CT_14</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-1.596393</v>
+        <v>-14.9599113986652</v>
       </c>
       <c r="D44" t="n">
-        <v>0.041338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CN6</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CD8 T cell</t>
+          <t>CT_15</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-1.596393</v>
+        <v>-4.00503045829747</v>
       </c>
       <c r="D45" t="n">
-        <v>0.041338</v>
+        <v>0.0029181963663748</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CN6</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CD4 T cell</t>
+          <t>CT_16</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-1.596393</v>
+        <v>-3.1930185205992</v>
       </c>
       <c r="D46" t="n">
-        <v>0.041338</v>
+        <v>0.0002824060999717</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CN6</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B cell</t>
+          <t>CT_17</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.062129</v>
+        <v>-3.77201341422784</v>
       </c>
       <c r="D47" t="n">
-        <v>0.522003</v>
+        <v>0.0004392983777338</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CN6</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Endothelial</t>
+          <t>CT_18</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.8795190000000001</v>
+        <v>-2.18282122377624</v>
       </c>
       <c r="D48" t="n">
-        <v>0.22997</v>
+        <v>0.0194546424424989</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CN6</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fibroblast</t>
+          <t>CT_19</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-1.596393</v>
+        <v>-1.85950356235313</v>
       </c>
       <c r="D49" t="n">
-        <v>0.041338</v>
+        <v>0.0023220057108789</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CN7</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tumor</t>
+          <t>CT_20</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-1.439384</v>
+        <v>-14.9599113986652</v>
       </c>
       <c r="D50" t="n">
-        <v>0.046091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CN7</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Stroma</t>
+          <t>CT_21</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-1.439384</v>
+        <v>-5.69850576110795</v>
       </c>
       <c r="D51" t="n">
-        <v>0.046091</v>
+        <v>6.27569111048354e-05</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CN7</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Macrophage</t>
+          <t>CT_22</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-1.439384</v>
+        <v>-3.0415226176416</v>
       </c>
       <c r="D52" t="n">
-        <v>0.046091</v>
+        <v>0.001506165866516</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CN7</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CD8 T cell</t>
+          <t>CT_23</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-1.439384</v>
+        <v>-14.9599113986652</v>
       </c>
       <c r="D53" t="n">
-        <v>0.046091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CN7</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CD4 T cell</t>
+          <t>CT_24</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-1.439384</v>
+        <v>-14.9599113986652</v>
       </c>
       <c r="D54" t="n">
-        <v>0.046091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CN7</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B cell</t>
+          <t>CT_25</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-1.439384</v>
+        <v>-14.9599113986652</v>
       </c>
       <c r="D55" t="n">
-        <v>0.046091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CN7</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Endothelial</t>
+          <t>CT_26</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2.100809</v>
+        <v>-8.18376962177809</v>
       </c>
       <c r="D56" t="n">
-        <v>0.536187</v>
+        <v>3.13784555524177e-05</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CN7</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fibroblast</t>
+          <t>CT_27</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.583186</v>
+        <v>-6.3746160359875</v>
       </c>
       <c r="D57" t="n">
-        <v>0.187269</v>
+        <v>0.0006275691110483</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CN8</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tumor</t>
+          <t>CT_00</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.517803</v>
+        <v>-1.84479567642892</v>
       </c>
       <c r="D58" t="n">
-        <v>0.178972</v>
+        <v>0.0522622699386503</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CN8</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Stroma</t>
+          <t>CT_01</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-1.484609</v>
+        <v>-1.05195479480929</v>
       </c>
       <c r="D59" t="n">
-        <v>0.044668</v>
+        <v>0.0007668711656441</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CN8</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Macrophage</t>
+          <t>CT_02</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-1.484609</v>
+        <v>-2.49961931981725</v>
       </c>
       <c r="D60" t="n">
-        <v>0.044668</v>
+        <v>0.0012653374233128</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CN8</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CD8 T cell</t>
+          <t>CT_03</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-1.484609</v>
+        <v>-0.983379227221853</v>
       </c>
       <c r="D61" t="n">
-        <v>0.044668</v>
+        <v>0.0562883435582822</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CN8</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CD4 T cell</t>
+          <t>CT_04</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-1.484609</v>
+        <v>-0.240508042993068</v>
       </c>
       <c r="D62" t="n">
-        <v>0.044668</v>
+        <v>0.001111963190184</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CN8</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B cell</t>
+          <t>CT_05</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-1.484609</v>
+        <v>-0.526880473056401</v>
       </c>
       <c r="D63" t="n">
-        <v>0.044668</v>
+        <v>0.0050230061349693</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CN8</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Endothelial</t>
+          <t>CT_06</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-1.484609</v>
+        <v>-0.436263505719487</v>
       </c>
       <c r="D64" t="n">
-        <v>0.044668</v>
+        <v>0.0192101226993865</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CN8</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fibroblast</t>
+          <t>CT_07</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2.145402</v>
+        <v>-0.586626392815445</v>
       </c>
       <c r="D65" t="n">
-        <v>0.553019</v>
+        <v>0.0443251533742331</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CN9</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tumor</t>
+          <t>CT_08</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2.252482</v>
+        <v>-0.654411830093162</v>
       </c>
       <c r="D66" t="n">
-        <v>0.595627</v>
+        <v>0.0423312883435582</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CN9</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Stroma</t>
+          <t>CT_09</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.542807</v>
+        <v>-0.293356036104803</v>
       </c>
       <c r="D67" t="n">
-        <v>0.182101</v>
+        <v>0.128796012269938</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CN9</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Macrophage</t>
+          <t>CT_10</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-1.754564</v>
+        <v>0.408863075166984</v>
       </c>
       <c r="D68" t="n">
-        <v>0.037045</v>
+        <v>0.0450920245398773</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CN9</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CD8 T cell</t>
+          <t>CT_11</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-1.754564</v>
+        <v>0.462024794539938</v>
       </c>
       <c r="D69" t="n">
-        <v>0.037045</v>
+        <v>0.0153374233128834</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CN9</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CD4 T cell</t>
+          <t>CT_12</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-1.754564</v>
+        <v>0.247564711715387</v>
       </c>
       <c r="D70" t="n">
-        <v>0.037045</v>
+        <v>0.0101993865030674</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CN9</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B cell</t>
+          <t>CT_13</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-1.754564</v>
+        <v>2.13688443220193</v>
       </c>
       <c r="D71" t="n">
-        <v>0.037045</v>
+        <v>0.353757668711656</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CN9</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Endothelial</t>
+          <t>CT_14</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-1.754564</v>
+        <v>0.60131523324784</v>
       </c>
       <c r="D72" t="n">
-        <v>0.037045</v>
+        <v>0.001111963190184</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>CN3</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CT_15</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1.20732092958797</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.108243865030674</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CN3</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CT_16</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1.04481014906752</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.0053297546012269</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>CN3</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CT_17</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.182199833351148</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.0052914110429447</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CN3</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CT_18</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.58866757518838</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.0587423312883435</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CN3</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CT_19</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.675440481295752</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.0134585889570552</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>CN3</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CT_20</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1.17603273082622</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.0029141104294478</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>CN3</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CT_21</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>-3.60363111938756</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.0002684049079754</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>CN3</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CT_22</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>-1.73756073685836</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.0037193251533742</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CN3</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CT_23</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>-14.6707115661193</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CN3</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CT_24</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1.18101949902047</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.0003450920245398</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CN3</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CT_25</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1.8465176909557</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.0027223926380368</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CN3</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CT_26</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>-1.20722569188928</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.0039877300613496</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CN3</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CT_27</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>-1.52830273316808</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.0180981595092024</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CT_00</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>-2.18766534860273</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.0412081890316075</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CT_01</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>-1.72122382683085</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.0004822234886677</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CT_02</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>-2.54354913676721</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.0012274779711542</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CT_03</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>-1.12866557608557</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.0508964973039323</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>CT_04</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.9052572942620279</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.0007014159835167</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CT_05</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0.859284317741874</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.0131296304414536</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CT_06</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0.112442519914739</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.0281004778396387</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CT_07</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.524640922025455</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.0462715356626189</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CT_08</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0.109723921215117</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.07189513831046419</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CT_09</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1.59890898376248</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.478124589014072</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CT_10</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0.465804913328956</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.0469071938976809</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CT_11</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0.317453383097086</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.0138748849239402</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CT_12</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0.43534548711281</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.0116172022269957</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CT_13</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.276715680229757</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.06639340668975489</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CT_14</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0.5512670703529829</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.0010740432247599</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CT_15</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.469977732021333</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.0338433212046819</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CT_16</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.341720980199151</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.0020384902020954</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CT_17</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.597655442969263</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.0039673841567664</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>CT_18</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.864216405044026</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.0485292183595633</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CT_19</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>0.0857716346628604</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.008943053789838199</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CT_20</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0.208808809250309</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.001490508964973</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CT_21</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.589016576836605</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.0021700056990048</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>CT_22</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.756349480153981</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.0073429485774407</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>CT_23</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.291886897208027</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.0002191924948489</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>CT_24</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0.789288769657131</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.0002630309938187</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CT_25</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>-1.10993868579121</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.0003507079917583</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>CT_26</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>-1.35692226276856</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.0035947569155232</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>CN4</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CT_27</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>-1.76654877105406</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.0153434746394283</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CT_00</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>-2.83768099458519</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.0262503883193538</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CT_01</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>0.103740966377826</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.001708605156881</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CT_02</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.718584343558536</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.0043491767629698</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CT_03</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>-3.56473261996895</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.009397328362845601</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CT_04</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>-2.07987799016099</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.0003106554830692</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>CT_05</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>-0.352212930278942</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.0056694625660142</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>CT_06</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.801644681426762</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.0149114631873252</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>CT_07</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0.356002866530585</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.08519726623174891</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>CT_08</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.0049276575876116</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.0664026095060577</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>CT_09</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>-2.60897521242944</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.0258620689655172</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>CT_10</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>-2.21753824448688</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.0073004038521279</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>CT_11</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>-1.80572514650989</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.00318421870146</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>CT_12</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>-2.26546091689182</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.0017862690276483</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>CT_13</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>-1.97705492643691</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.0204255980118049</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CT_14</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>-2.23797094977891</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.0001553277415346</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CT_15</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>-1.31242299354474</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.0188723205964585</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CT_16</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>-2.24806782654183</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.0005436470953712001</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>CT_17</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>-3.27150210156448</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.0006213109661385</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>CT_18</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>-2.6511988227249</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.0140571606088847</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>CT_19</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>-1.95392966241005</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.0021745883814849</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>CT_20</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>-4.05185721119862</v>
+      </c>
+      <c r="D134" t="n">
+        <v>7.7663870767319e-05</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>CT_21</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>-2.39286743476093</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.0006213109661385</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>CT_22</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>-1.29681229283311</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.0050481515998757</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>CT_23</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>-1.78850182348416</v>
+      </c>
+      <c r="D137" t="n">
+        <v>7.7663870767319e-05</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>CT_24</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>0.0293825466067871</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.0001553277415346</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>CT_25</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>0.415481575939746</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.0010096303199751</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>CT_26</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1.7757781636364</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.0315315315315315</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>CN5</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>CT_27</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>3.64310813609945</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.652298850574712</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>CT_00</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1.12307146154613</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.4089392342817</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CT_01</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1.42136035514533</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.0042588689848963</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CT_02</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>2.69276409050744</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.0462767825781524</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CT_03</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>-1.43562681955545</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.0411397962767825</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>CT_04</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.443615179226824</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.0009659290481208</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>CT_05</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>0.541972370569511</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.0105374077976817</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>CT_06</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>0.469942129692524</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0.0360028099754127</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>CT_07</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>-1.01726358124883</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0.0328854935019318</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>CT_08</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.543755217473469</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.0457060063224446</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>CT_09</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.63492362058457</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.101642079381805</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>CT_10</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>-1.02165369925069</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0.0167281348788198</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>CT_11</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>0.340029421851828</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.0140937829293993</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>CT_12</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>0.142602010876354</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.0094836670179135</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>CT_13</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.217986488644405</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.06915173867228661</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>CT_14</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>-1.06114860621735</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.0003512469265893</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>CT_15</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.290379684736794</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.0383298208640674</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CT_16</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.971721466985399</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.0013171759747102</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CT_17</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.57170950633853</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0.004039339655778</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>CT_18</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.14236114307681</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.0800403933965577</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>CT_19</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1.14004266567402</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0.0185721812434141</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>CT_20</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>-1.41689706377897</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.0004829645240604</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>CT_21</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>-1.21609003123791</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0.0014049877063575</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>CT_22</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.6422918544374761</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.007946961714085</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>CT_23</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>-14.4752901191266</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>CT_24</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>-1.79328889641418</v>
+      </c>
+      <c r="D166" t="n">
+        <v>4.3905865823674e-05</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>CT_25</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.937777023927448</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0.000395152792413</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>CT_26</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>-2.39011152942927</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0.0017562346329469</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>CN6</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>CT_27</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>-2.7973909907287</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0.0075079030558482</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>CT_00</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>-2.3237818453324</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.0374953130858642</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>CT_01</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>-1.31867254103088</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.0006374203224596</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>CT_02</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>-2.82132915214856</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0.0010123734533183</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CT_03</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>1.76554282000554</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.378402699662542</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>CT_04</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>2.02905746832618</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.0053618297712785</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>CT_05</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.463298312822425</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.0052493438320209</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>CT_06</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>-1.04484885262383</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0.0125984251968503</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>CT_07</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.65171583828461</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0.0423697037870266</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>CT_08</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.313429435529722</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0.0536182977127859</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>CT_09</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.35250540150608</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.123622047244094</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>CT_10</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.103676722054972</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0.0316085489313835</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>CT_11</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>0.0805276205666068</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0.0117735283089613</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>CT_12</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.430573207837638</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.0063742032245969</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>CT_13</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.0696542037174538</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0.07664041994750651</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>CT_14</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>0.7554512062702901</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.0012373453318335</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>CT_15</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1.0908729370675</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.0998500187476565</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>CT_16</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>1.15098173403114</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.0057367829021372</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>CT_17</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1.76441897787314</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0.0203974503187101</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>CT_18</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.575521814591118</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.0592800899887514</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>CT_19</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.499234691842156</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0.0059617547806524</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>CT_20</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>-2.1039594407213</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0.0002999625046869</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>CT_21</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>-1.44378420983769</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.0011998500187476</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>CT_22</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>-2.7845955167028</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0.0017997750281214</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>CT_23</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>-14.7029842977264</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>CT_24</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>0.563796464904106</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0.0002249718785151</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>CT_25</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>-2.33524454635636</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0.0001499812523434</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>CT_26</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>-3.29567841075037</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0.0009373828271466</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>CN7</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>CT_27</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>-1.69165927687255</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0.0161604799400074</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>CT_00</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>-3.1850681581657</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.0206309819213045</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>CT_01</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>-2.90158039150928</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.0002126905352711</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>CT_02</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>-3.48656421933482</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0.0006380716058135</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>CT_03</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>2.79879368944509</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0.774477135767458</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>CT_04</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>1.24761054343223</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0.0031194611839773</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>CT_05</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>-1.38802301649691</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0.0027649769585253</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>CT_06</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>-2.93257135375881</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0.0034030485643388</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>CT_07</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>-2.58892721512731</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.0110599078341013</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>CT_08</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>-1.82612186821093</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0.0187876639489542</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>CT_09</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>-1.63843178759658</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0.0506912442396313</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>CT_10</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>-2.41176326282405</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.0063807160581354</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>CT_11</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>-1.6510038883966</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.0035448422545196</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>CT_12</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>-2.27672220025141</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.0017724211272598</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>CT_13</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>-1.3179497386736</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0.032258064516129</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>CT_14</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>-0.784873256505923</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0.0004253810705423</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>CT_15</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>-0.529674757484622</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0.0324707550514002</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>CT_16</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>-0.432441963400984</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0.0019142148174406</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>CT_17</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>-0.08206045164491289</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.0056717476072314</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>CT_18</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>-2.07825799070943</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0.020914569301666</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>CT_19</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>-2.24888873021749</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.0017724211272598</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>CT_20</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>-13.7840213243741</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>CT_21</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>-2.71694087764243</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0.0004962779156327</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>CT_22</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>-4.27905582856331</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0.0006380716058135</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>CT_23</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>-13.7840213243741</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>CT_24</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>-1.10202010166172</v>
+      </c>
+      <c r="D222" t="n">
+        <v>7.08968450903934e-05</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>CT_25</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>-13.7840213243741</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>CT_26</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>-5.43171913103926</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0.0002126905352711</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CN8</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>CT_27</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>-3.20154582944086</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0.0056717476072314</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
           <t>CN9</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Fibroblast</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>-1.754564</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0.037045</v>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>CT_00</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>-1.70654301360546</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.0575179889729931</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>CT_01</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>0.955617450119212</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.0030838239416876</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>CT_02</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>-2.67374747420313</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.00112139052425</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>CT_03</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>-1.75827902366493</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.0328941220446687</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>CT_04</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>-0.906351292637979</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.0007008690776562</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>CT_05</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>-2.63092324016975</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.0011681151294271</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>CT_06</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>-1.33174675577188</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.010326137744136</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>CT_07</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>-1.25711934778444</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.0278478646855434</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CT_08</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>-1.09831450425735</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0.0311185870479394</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>CT_09</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>-0.626552656722218</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0.102233436127464</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>CT_10</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>-0.84020817787734</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.018970189701897</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>CT_11</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>0.365461772218304</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0.0143444537893654</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>CT_12</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>0.135694678356507</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.0094383702457714</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>CT_13</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>-0.649977980627279</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0.0512568918792636</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>CT_14</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>-0.270995011403513</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.0006074198673021</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>CT_15</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>-0.515106728978856</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.0328006728343145</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>CT_16</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>-0.6189430546574241</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.0016820857863751</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>CT_17</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>1.28904743669034</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.014671526025605</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>CT_18</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>2.63819490644085</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.549995327539482</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>CT_19</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>1.00514425276161</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.0169143070741052</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>CT_20</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>-1.97911241086485</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.0003270722362396</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>CT_21</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>-1.804308939438</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.0009344921035417</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>CT_22</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>-3.4667639566683</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.00112139052425</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>CT_23</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>-2.52151833004534</v>
+      </c>
+      <c r="D249" t="n">
+        <v>4.67246051770862e-05</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>CT_24</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>-14.3855254089693</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>CT_25</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>-1.43291414953295</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.0002803476310625</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>CT_26</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>-1.28259298406711</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.0037846930193439</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>CN9</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>CT_27</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>-1.81734258062756</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.0148116998411363</v>
       </c>
     </row>
   </sheetData>
